--- a/config/Group list.xlsx
+++ b/config/Group list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lutfi\Tech\scrapper\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lutfi\Tech\fb-group-seller-scraper\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65332DF-5584-4D5A-8340-D1225DBA25B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4BC6DE-91CA-4299-8BD4-2C642AF8C07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{3ABA4855-2133-4113-8E5F-F8A5B4857855}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>https://www.facebook.com/groups/1499355573871027/?sorting_setting=CHRONOLOGICAL</t>
   </si>
   <si>
-    <t>https://web.facebook.com/groups/2632178413729281/</t>
-  </si>
-  <si>
     <t>KURIR POLMAN 🛵🌏</t>
   </si>
   <si>
@@ -95,40 +92,43 @@
     <t>Polman Dagang Segalanya</t>
   </si>
   <si>
-    <t>https://web.facebook.com/groups/804859393256050/?sorting_setting=CHRONOLOGICAL_LISTINGS</t>
-  </si>
-  <si>
     <t>POLMAN DAGANG</t>
   </si>
   <si>
     <t>Polewali Mandar Online Shop</t>
   </si>
   <si>
-    <t>http://web.facebook.com/groups/843685739055107/?sorting_setting=CHRONOLOGICAL_LISTINGS</t>
-  </si>
-  <si>
     <t>https://web.facebook.com/groups/287884132890468/?sorting_setting=CHRONOLOGICAL</t>
   </si>
   <si>
     <t>POLEWALI DAGANG</t>
   </si>
   <si>
-    <t>https://web.facebook.com/groups/1073186462716139/?sorting_setting=CHRONOLOGICAL_LISTINGS</t>
-  </si>
-  <si>
     <t>HP Bekas Polman</t>
   </si>
   <si>
-    <t>https://web.facebook.com/groups/232129577241617/?sorting_setting=CHRONOLOGICAL_LISTINGS</t>
-  </si>
-  <si>
     <t>TINAMBUNG DAGANG</t>
   </si>
   <si>
     <t>https://web.facebook.com/groups/584543845568268/</t>
   </si>
   <si>
-    <t>https://web.facebook.com/groups/393506048155774/?sorting_setting=CHRONOLOGICAL_LISTINGS</t>
+    <t>https://web.facebook.com/groups/2632178413729281/?sorting_setting=CHRONOLOGICAL</t>
+  </si>
+  <si>
+    <t>https://web.facebook.com/groups/804859393256050/</t>
+  </si>
+  <si>
+    <t>https://web.facebook.com/groups/393506048155774/?sorting_setting=RECENT_LISTING_ACTIVITY</t>
+  </si>
+  <si>
+    <t>https://web.facebook.com/groups/232129577241617/?sorting_setting=RECENT_LISTING_ACTIVITY</t>
+  </si>
+  <si>
+    <t>http://web.facebook.com/groups/843685739055107/?sorting_setting=RECENT_LISTING_ACTIVITY</t>
+  </si>
+  <si>
+    <t>https://web.facebook.com/groups/1073186462716139/?sorting_setting=RECENT_LISTING_ACTIVITY</t>
   </si>
 </sst>
 </file>
@@ -544,10 +544,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -560,98 +560,98 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -665,12 +665,12 @@
     <hyperlink ref="B8" r:id="rId7" xr:uid="{E59E0C78-DE26-4778-877A-D0A71B9C0458}"/>
     <hyperlink ref="B4" r:id="rId8" xr:uid="{753E2753-760F-492D-9832-9CBA0649BD21}"/>
     <hyperlink ref="B5" r:id="rId9" xr:uid="{C889FDAB-DD87-40AA-A5A9-D83D9B674D17}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{9A59D7DE-E11B-4D9F-B634-A1F40F6CFC78}"/>
-    <hyperlink ref="B15" r:id="rId11" xr:uid="{CD9F7D61-880A-49CC-819E-8EAB4855EB1A}"/>
-    <hyperlink ref="B14" r:id="rId12" xr:uid="{0DCC1ACC-71DD-47F9-9053-969A7E5F4392}"/>
-    <hyperlink ref="B16" r:id="rId13" xr:uid="{251339F2-82D3-4F9A-A8B4-DE447953D90A}"/>
-    <hyperlink ref="B7" r:id="rId14" xr:uid="{7C5D972C-6CA1-4C03-BE08-CB22200C64A1}"/>
-    <hyperlink ref="B9" r:id="rId15" xr:uid="{11A01DCF-2B98-4CB0-A96A-700DC37E79EB}"/>
+    <hyperlink ref="B15" r:id="rId10" xr:uid="{CD9F7D61-880A-49CC-819E-8EAB4855EB1A}"/>
+    <hyperlink ref="B16" r:id="rId11" xr:uid="{251339F2-82D3-4F9A-A8B4-DE447953D90A}"/>
+    <hyperlink ref="B7" r:id="rId12" xr:uid="{7C5D972C-6CA1-4C03-BE08-CB22200C64A1}"/>
+    <hyperlink ref="B9" r:id="rId13" xr:uid="{11A01DCF-2B98-4CB0-A96A-700DC37E79EB}"/>
+    <hyperlink ref="B11" r:id="rId14" xr:uid="{E558DDB2-E036-4F72-8EDA-1CAC03D8ADD6}"/>
+    <hyperlink ref="B10" r:id="rId15" xr:uid="{4AB92C45-21E5-468F-B7B7-351D77981890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId16"/>
